--- a/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FB3AC4-ECA3-4EBA-A44F-E2758A2BC056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D548CB84-5F21-41E1-A79A-8E05B32FFF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1477,12 +1477,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1171575</xdr:colOff>
+      <xdr:colOff>1162050</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
@@ -1499,8 +1499,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="609600" y="3076575"/>
-          <a:ext cx="4067175" cy="5829300"/>
+          <a:off x="609600" y="2847975"/>
+          <a:ext cx="4057650" cy="6057900"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>

--- a/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D548CB84-5F21-41E1-A79A-8E05B32FFF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468BBBC0-D4D5-44CA-8FAB-1D87F688150B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2026" sheetId="12" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="JUILLET 2026" sheetId="18" r:id="rId7"/>
     <sheet name="AOUT 2026" sheetId="19" r:id="rId8"/>
     <sheet name="SEPTEMBRE 2026" sheetId="20" r:id="rId9"/>
+    <sheet name="OCTOBRE 2026" sheetId="21" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'AOUT 2026'!$1:$6</definedName>
@@ -32,6 +33,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'JUIN 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'MARS 2026'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'OCTOBRE 2026'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'SEPTEMBRE 2026'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="175">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -771,6 +773,42 @@
   <si>
     <t>NB(255/2026)</t>
   </si>
+  <si>
+    <r>
+      <t>Mois de OCTOBRE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2026</t>
+    </r>
+  </si>
+  <si>
+    <t>641153</t>
+  </si>
+  <si>
+    <t>2026143437</t>
+  </si>
+  <si>
+    <t>640340</t>
+  </si>
+  <si>
+    <t>2026143438</t>
+  </si>
 </sst>
 </file>
 
@@ -1061,6 +1099,61 @@
         <a:xfrm flipH="1">
           <a:off x="609600" y="4381500"/>
           <a:ext cx="4048125" cy="4524375"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Connecteur droit 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E2B73EE-5080-4660-8AF2-11C612CBE8CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="609600" y="2847975"/>
+          <a:ext cx="4057650" cy="6057900"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3544,6 +3637,1562 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E011D6AC-FA26-4ACD-AA15-6BFC0C8286C7}">
+  <dimension ref="A1:K97"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="16">
+        <f ca="1">SUMIF(F7:F316,"Elimination*",G7:G136)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="16">
+        <f>SUMIF(F7:F136,"NB*",G7:G136)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16">
+        <f>SUMIF(F7:F136,"Ve*",G7:G136)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="18">
+        <f ca="1">SUM(K2:K4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>1</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="12">
+        <v>46299</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <f t="shared" ref="A8:A71" si="0">+A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46299</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="15">
+        <v>1</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="15">
+        <v>1</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="15">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="15">
+        <v>1</v>
+      </c>
+      <c r="H13" s="20"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="15">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="15">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="15">
+        <v>1</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="15">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="15">
+        <v>1</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="15">
+        <v>1</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="15">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="15">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="15">
+        <v>1</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B42" s="9"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="14">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="14">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="14">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="14">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="14">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="14">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="14">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="14">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="14">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="14">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="14">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="14">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="14">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="14">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="14">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="14">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="14">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B63" s="9"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="14">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="14">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="14">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B66" s="9"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="14">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="14">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B68" s="9"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="14">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B69" s="9"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="14">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="14">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="14">
+        <f t="shared" ref="A72:A97" si="1">+A71+1</f>
+        <v>66</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="14">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="14">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="14">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="14">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B76" s="9"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="14">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B77" s="9"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="14">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B78" s="9"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="14">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="14">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="14">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="14">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B82" s="9"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="14">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B83" s="9"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="14">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="14">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B85" s="9"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="14">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B86" s="9"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="14">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B87" s="9"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="14">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B88" s="9"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="14">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B89" s="9"/>
+      <c r="C89" s="10"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="14">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="14">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B91" s="9"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="19"/>
+      <c r="G91" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="14">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="14">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B93" s="9"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="19"/>
+      <c r="G93" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="14">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B94" s="9"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="14">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B95" s="9"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="14">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="14">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B97" s="9"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="15">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="180" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3129568E-FA8F-41F3-ACBA-9E5FA11A3FB3}">
   <dimension ref="A1:K97"/>

--- a/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468BBBC0-D4D5-44CA-8FAB-1D87F688150B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29F84DA-B7D2-414C-9347-E7CF477D7DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="198">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -808,6 +808,75 @@
   </si>
   <si>
     <t>2026143438</t>
+  </si>
+  <si>
+    <t>2026003383</t>
+  </si>
+  <si>
+    <t>NB(384/2026)</t>
+  </si>
+  <si>
+    <t>Chabira samir</t>
+  </si>
+  <si>
+    <t>2026003386</t>
+  </si>
+  <si>
+    <t>Chouihi boulanouar</t>
+  </si>
+  <si>
+    <t>NB(371/2025)</t>
+  </si>
+  <si>
+    <t>2026003385</t>
+  </si>
+  <si>
+    <t>Boukoufalah lakhdar</t>
+  </si>
+  <si>
+    <t>NB(283/2025)</t>
+  </si>
+  <si>
+    <t>2026003390</t>
+  </si>
+  <si>
+    <t>Belmihoub abdelhak</t>
+  </si>
+  <si>
+    <t>NB(361/2026)</t>
+  </si>
+  <si>
+    <t>2026003440</t>
+  </si>
+  <si>
+    <t>Kouidri a/azziz</t>
+  </si>
+  <si>
+    <t>NB(422/2026)</t>
+  </si>
+  <si>
+    <t>2026003382</t>
+  </si>
+  <si>
+    <t>Lalmaya aissa</t>
+  </si>
+  <si>
+    <t>NB(421/2026)</t>
+  </si>
+  <si>
+    <t>2026003381</t>
+  </si>
+  <si>
+    <t>Adjroud rafik</t>
+  </si>
+  <si>
+    <t>NB(542/2025)</t>
+  </si>
+  <si>
+    <t>640771</t>
+  </si>
+  <si>
+    <t>2026144377</t>
   </si>
 </sst>
 </file>
@@ -1130,12 +1199,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:colOff>1152525</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
@@ -1152,8 +1221,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="609600" y="2847975"/>
-          <a:ext cx="4057650" cy="6057900"/>
+          <a:off x="609600" y="3238500"/>
+          <a:ext cx="4048125" cy="5667375"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3687,7 +3756,7 @@
       <c r="J2" s="23"/>
       <c r="K2" s="16">
         <f ca="1">SUMIF(F7:F316,"Elimination*",G7:G136)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -3709,7 +3778,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F136,"NB*",G7:G136)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -3749,7 +3818,7 @@
       <c r="J5" s="23"/>
       <c r="K5" s="18">
         <f ca="1">SUM(K2:K4)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3839,15 +3908,27 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="19"/>
+      <c r="B9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46308</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>176</v>
+      </c>
       <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="H9" s="20" t="s">
+        <v>177</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
@@ -3857,15 +3938,27 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="19"/>
+      <c r="B10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46308</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>183</v>
+      </c>
       <c r="G10" s="15">
         <v>1</v>
       </c>
-      <c r="H10" s="20"/>
+      <c r="H10" s="20" t="s">
+        <v>182</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="1"/>
@@ -3875,15 +3968,27 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46308</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>180</v>
+      </c>
       <c r="G11" s="15">
         <v>1</v>
       </c>
-      <c r="H11" s="20"/>
+      <c r="H11" s="20" t="s">
+        <v>179</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="1"/>
@@ -3893,15 +3998,27 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46308</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="G12" s="15">
         <v>1</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="1"/>
@@ -3911,15 +4028,27 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46309</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>195</v>
+      </c>
       <c r="G13" s="15">
         <v>1</v>
       </c>
-      <c r="H13" s="20"/>
+      <c r="H13" s="20" t="s">
+        <v>194</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
@@ -3929,15 +4058,27 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46309</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>192</v>
+      </c>
       <c r="G14" s="15">
         <v>1</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>191</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
@@ -3946,15 +4087,27 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46309</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>189</v>
+      </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="H15" s="20"/>
+      <c r="H15" s="20" t="s">
+        <v>188</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
     </row>
@@ -3963,11 +4116,21 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46309</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>73</v>
+      </c>
       <c r="G16" s="15">
         <v>1</v>
       </c>
@@ -5170,6 +5333,10 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H16">
+    <sortCondition ref="E7:E16"/>
+    <sortCondition ref="D7:D16"/>
+  </sortState>
   <mergeCells count="11">
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="I4:J4"/>

--- a/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
+++ b/Gestion Stock 2026/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2026\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29F84DA-B7D2-414C-9347-E7CF477D7DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2EA44E6-0104-4069-8152-628546AF3876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="201">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -877,6 +877,15 @@
   </si>
   <si>
     <t>2026144377</t>
+  </si>
+  <si>
+    <t>2026003439</t>
+  </si>
+  <si>
+    <t>Chouihi ali</t>
+  </si>
+  <si>
+    <t>NB(484/2026)</t>
   </si>
 </sst>
 </file>
@@ -1199,12 +1208,12 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1152525</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
@@ -1221,8 +1230,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="609600" y="3238500"/>
-          <a:ext cx="4048125" cy="5667375"/>
+          <a:off x="609600" y="3457575"/>
+          <a:ext cx="4076700" cy="5448300"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3778,7 +3787,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="16">
         <f>SUMIF(F7:F136,"NB*",G7:G136)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
@@ -3818,7 +3827,7 @@
       <c r="J5" s="23"/>
       <c r="K5" s="18">
         <f ca="1">SUM(K2:K4)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -4143,15 +4152,27 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="19"/>
+      <c r="B17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="12">
+        <v>46313</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="G17" s="15">
         <v>1</v>
       </c>
-      <c r="H17" s="20"/>
+      <c r="H17" s="20" t="s">
+        <v>199</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
